--- a/summer_camp_application_forms/042_royal_family_kids_camp_application_form--summer_camp_application_forms.xlsx
+++ b/summer_camp_application_forms/042_royal_family_kids_camp_application_form--summer_camp_application_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'new_camper',_'label':_'new_camper'}</t>
+          <t>new_camper</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'New Camper', 'label': 'New Camper'}</t>
+          <t>New Camper</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'returning_camper',_'label':_'returning_camper'}</t>
+          <t>returning_camper</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Returning Camper', 'label': 'Returning Camper'}</t>
+          <t>Returning Camper</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'returning_camper_with_experience',_'label':_'returning_camper_with_experience'}</t>
+          <t>returning_camper_with_experience</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Returning Camper with Experience', 'label': 'Returning Camper with Experience'}</t>
+          <t>Returning Camper with Experience</t>
         </is>
       </c>
     </row>
